--- a/4993_Intercuenca_Medio_Bajo_Ucayali/_raw_reportes_xlsx/IDConfig_65105_completo.xlsx
+++ b/4993_Intercuenca_Medio_Bajo_Ucayali/_raw_reportes_xlsx/IDConfig_65105_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R608ee23d83194c25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R218af7c177794bee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,471 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>15:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>08/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4993_Intercuenca_Medio_Bajo_Ucayali/_raw_reportes_xlsx/IDConfig_65105_completo.xlsx
+++ b/4993_Intercuenca_Medio_Bajo_Ucayali/_raw_reportes_xlsx/IDConfig_65105_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R218af7c177794bee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R06f88995e03a4e66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,1446 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>11:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>16:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>08:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>07:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>09:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>19:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    200.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>17:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>20/08/2026</x:t>
         </x:is>
       </x:c>
